--- a/design/tables/ShopStaff.xlsx
+++ b/design/tables/ShopStaff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopStaff" sheetId="1" r:id="Rd6b0f66b4b794c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopStaff" sheetId="1" r:id="R6ee250cc5cf544b4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -293,6 +293,12 @@
       <x:c r="G1" s="1" t="str">
         <x:v>descriptionKey</x:v>
       </x:c>
+      <x:c r="H1" t="str">
+        <x:v>role</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>roleKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -314,6 +320,12 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -339,15 +351,41 @@
       <x:c r="G3" s="1" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="H3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="str"/>
-      <x:c r="G4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>staffKey</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>cost</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>effect</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>value</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="str">
+        <x:v>descriptionKey</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>role</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>roleKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -371,6 +409,12 @@
       <x:c r="G5" s="3" t="str">
         <x:v>descriptionKey</x:v>
       </x:c>
+      <x:c r="H5" t="str">
+        <x:v>role</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>roleKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="1" t="n">
@@ -394,6 +438,12 @@
       <x:c r="G6" s="1" t="str">
         <x:v>shop.staff.sprout</x:v>
       </x:c>
+      <x:c r="H6" t="str">
+        <x:v>cashier</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>shop.role.cashier</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1" t="n">
@@ -417,6 +467,12 @@
       <x:c r="G7" s="1" t="str">
         <x:v>shop.staff.frost</x:v>
       </x:c>
+      <x:c r="H7" t="str">
+        <x:v>cold</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>shop.role.cold</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="1" t="n">
@@ -440,6 +496,12 @@
       <x:c r="G8" s="1" t="str">
         <x:v>shop.staff.bloom</x:v>
       </x:c>
+      <x:c r="H8" t="str">
+        <x:v>pack</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>shop.role.pack</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="1" t="n">
@@ -463,6 +525,12 @@
       <x:c r="G9" s="1" t="str">
         <x:v>shop.staff.scope</x:v>
       </x:c>
+      <x:c r="H9" t="str">
+        <x:v>guide</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>shop.role.guide</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="1" t="n">
@@ -486,6 +554,12 @@
       <x:c r="G10" s="1" t="str">
         <x:v>shop.staff.spark</x:v>
       </x:c>
+      <x:c r="H10" t="str">
+        <x:v>tidy</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>shop.role.tidy</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="1" t="n">
@@ -509,6 +583,12 @@
       <x:c r="G11" s="1" t="str">
         <x:v>shop.staff.ember</x:v>
       </x:c>
+      <x:c r="H11" t="str">
+        <x:v>hot</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>shop.role.hot</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="1" t="n">
@@ -532,6 +612,12 @@
       <x:c r="G12" s="1" t="str">
         <x:v>shop.staff.mint</x:v>
       </x:c>
+      <x:c r="H12" t="str">
+        <x:v>porter</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>shop.role.porter</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="1" t="n">
@@ -554,6 +640,12 @@
       </x:c>
       <x:c r="G13" s="1" t="str">
         <x:v>shop.staff.fan</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>welcome</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>shop.role.welcome</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
